--- a/data/trans_dic/P64D$noloshace_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,3</t>
+          <t>0,59; 7,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,23</t>
+          <t>1,8; 9,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,17</t>
+          <t>1,57; 6,27</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,35</t>
+          <t>1,01; 3,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,83</t>
+          <t>1,86; 3,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,2</t>
+          <t>1,49; 3,21</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,8</t>
+          <t>6,48; 12,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,5</t>
+          <t>3,65; 7,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,41</t>
+          <t>5,76; 9,49</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,96</t>
+          <t>2,43; 5,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,59</t>
+          <t>2,78; 4,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,5</t>
+          <t>2,89; 4,56</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>886; 9638</t>
+          <t>773; 9950</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1295; 6620</t>
+          <t>1452; 7321</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3363; 13105</t>
+          <t>3333; 13330</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14564; 46252</t>
+          <t>13982; 46913</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17250; 36206</t>
+          <t>17591; 37144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36435; 74489</t>
+          <t>34662; 74706</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27234; 57233</t>
+          <t>28985; 57249</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15824; 32652</t>
+          <t>15878; 33010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49197; 83070</t>
+          <t>50803; 83748</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45412; 97309</t>
+          <t>47733; 98229</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40183; 67027</t>
+          <t>40576; 67644</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95319; 154159</t>
+          <t>98949; 156137</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$noloshace_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,53</t>
+          <t>0,68; 6,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 9,1</t>
+          <t>2,64; 10,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,27</t>
+          <t>2,0; 6,47</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,39</t>
+          <t>1,71; 3,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,93</t>
+          <t>2,42; 4,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,21</t>
+          <t>2,26; 3,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 12,8</t>
+          <t>7,07; 13,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,58</t>
+          <t>3,73; 7,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,49</t>
+          <t>6,04; 9,96</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,01</t>
+          <t>3,47; 5,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,63</t>
+          <t>3,3; 5,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,56</t>
+          <t>3,7; 5,16</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>9345</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>773; 9950</t>
+          <t>1107; 10898</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1452; 7321</t>
+          <t>2319; 9170</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3333; 13330</t>
+          <t>5039; 16300</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54663</t>
+          <t>64719</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13982; 46913</t>
+          <t>21696; 47317</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17591; 37144</t>
+          <t>22902; 43035</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34662; 74706</t>
+          <t>50097; 82836</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>48728</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64295</t>
+          <t>74788</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28985; 57249</t>
+          <t>34448; 64918</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15878; 33010</t>
+          <t>17824; 36220</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50803; 83748</t>
+          <t>58285; 96101</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>148852</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47733; 98229</t>
+          <t>66607; 107011</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40576; 67644</t>
+          <t>49842; 77526</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98949; 156137</t>
+          <t>126935; 177086</t>
         </is>
       </c>
     </row>
